--- a/data/trans_orig/P2A_fisi_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P2A_fisi_R-Edad-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4843</t>
+          <t>4527</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3905</t>
+          <t>4006</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>683</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5599</t>
+          <t>6276</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>73716</t>
+          <t>74032</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>84559</t>
+          <t>84458</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>161424</t>
+          <t>160747</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>167023</t>
+          <t>166340</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,59%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>578</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5550</t>
+          <t>4946</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4055</t>
+          <t>4179</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13575</t>
+          <t>13686</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5256</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15266</t>
+          <t>15335</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>181696</t>
+          <t>182300</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>186667</t>
+          <t>186668</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>175156</t>
+          <t>175045</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>184676</t>
+          <t>184552</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>360711</t>
+          <t>360642</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>370721</t>
+          <t>370640</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,58%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3914</t>
+          <t>4434</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2733</t>
+          <t>2702</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10402</t>
+          <t>10614</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2920</t>
+          <t>3347</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11578</t>
+          <t>11725</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,18%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>82565</t>
+          <t>82045</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>92859</t>
+          <t>92647</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>100528</t>
+          <t>100559</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>178162</t>
+          <t>178015</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>186820</t>
+          <t>186393</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,24%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2261</t>
+          <t>2154</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9923</t>
+          <t>9608</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1921</t>
+          <t>1898</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8734</t>
+          <t>8891</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5338</t>
+          <t>5517</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15449</t>
+          <t>15181</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,07%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>141152</t>
+          <t>141467</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>148814</t>
+          <t>148921</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>139360</t>
+          <t>139203</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>146173</t>
+          <t>146196</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>283720</t>
+          <t>283988</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>293831</t>
+          <t>293652</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,16%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4835</t>
+          <t>5012</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14749</t>
+          <t>15030</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11828</t>
+          <t>12140</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25565</t>
+          <t>26620</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20139</t>
+          <t>19548</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>37367</t>
+          <t>36688</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>488610</t>
+          <t>488329</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>498524</t>
+          <t>498347</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>502984</t>
+          <t>501929</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>516721</t>
+          <t>516409</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>994541</t>
+          <t>995220</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1011769</t>
+          <t>1012360</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,11%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1245</t>
+          <t>1208</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7518</t>
+          <t>6917</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>590</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5058</t>
+          <t>4632</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2512</t>
+          <t>2479</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10102</t>
+          <t>9763</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>96603</t>
+          <t>97204</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>102876</t>
+          <t>102913</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>106985</t>
+          <t>107411</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>112043</t>
+          <t>111453</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>206061</t>
+          <t>206400</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>213651</t>
+          <t>213684</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,85%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1875</t>
+          <t>1894</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10081</t>
+          <t>10299</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2821</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10707</t>
+          <t>10955</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6166</t>
+          <t>6123</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17558</t>
+          <t>17135</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>149263</t>
+          <t>149045</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>157469</t>
+          <t>157450</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>182517</t>
+          <t>182269</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>190621</t>
+          <t>190403</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>335010</t>
+          <t>335433</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>346402</t>
+          <t>346445</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,26%</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4737</t>
+          <t>4740</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>773</t>
+          <t>844</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6787</t>
+          <t>7588</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1486</t>
+          <t>1589</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8638</t>
+          <t>9442</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,73%</t>
         </is>
       </c>
     </row>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>93243</t>
+          <t>93240</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>95025</t>
+          <t>94224</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>101039</t>
+          <t>100968</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>191155</t>
+          <t>190351</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>198307</t>
+          <t>198204</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,2%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1557</t>
+          <t>1417</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8367</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4596</t>
+          <t>4608</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14572</t>
+          <t>13953</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7939</t>
+          <t>7619</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19388</t>
+          <t>18868</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,63%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>107153</t>
+          <t>107424</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>113963</t>
+          <t>114103</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>117130</t>
+          <t>117749</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>127106</t>
+          <t>127094</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>227833</t>
+          <t>228353</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>239282</t>
+          <t>239602</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,92%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8417</t>
+          <t>8595</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21328</t>
+          <t>20541</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13359</t>
+          <t>12767</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27717</t>
+          <t>27542</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>23632</t>
+          <t>24241</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>41632</t>
+          <t>42138</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>455637</t>
+          <t>456424</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>468548</t>
+          <t>468370</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>511064</t>
+          <t>511239</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>525422</t>
+          <t>526014</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>974114</t>
+          <t>973608</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>992114</t>
+          <t>991505</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,61%</t>
         </is>
       </c>
     </row>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>2622</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3869</t>
+          <t>3241</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4702,7 +4702,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4809</t>
+          <t>4151</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4717,7 +4717,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>99522</t>
+          <t>100082</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4775,7 +4775,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>94398</t>
+          <t>95026</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>196162</t>
+          <t>196820</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>573</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8187</t>
+          <t>6750</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1194</t>
+          <t>1190</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6904</t>
+          <t>7022</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2977</t>
+          <t>2985</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11426</t>
+          <t>11730</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>148078</t>
+          <t>149515</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>155319</t>
+          <t>155692</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>203688</t>
+          <t>203570</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>209398</t>
+          <t>209402</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>355431</t>
+          <t>355127</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>363880</t>
+          <t>363872</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,7 +5168,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2192</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9284</t>
+          <t>10101</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>594</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5108</t>
+          <t>5622</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>3432</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12032</t>
+          <t>12379</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,48%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>135030</t>
+          <t>134213</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>142122</t>
+          <t>142297</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>127063</t>
+          <t>126549</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>131581</t>
+          <t>131577</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>264453</t>
+          <t>264106</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>273035</t>
+          <t>273053</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,76%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2118</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11457</t>
+          <t>11039</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2827</t>
+          <t>2966</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12876</t>
+          <t>12475</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7084</t>
+          <t>7101</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19058</t>
+          <t>19969</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,92%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>110649</t>
+          <t>111067</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>119988</t>
+          <t>119639</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>117128</t>
+          <t>117529</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>127177</t>
+          <t>127038</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>233052</t>
+          <t>232141</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>245026</t>
+          <t>245009</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,18%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8157</t>
+          <t>8253</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21193</t>
+          <t>21186</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,7 +6014,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7533</t>
+          <t>7317</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18987</t>
+          <t>19810</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>36896</t>
+          <t>36956</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>504197</t>
+          <t>504204</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>517233</t>
+          <t>517137</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>552046</t>
+          <t>551223</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>563500</t>
+          <t>563716</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,7 +6182,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1059527</t>
+          <t>1059467</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>898</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5289</t>
+          <t>4923</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6614,7 +6614,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1938</t>
+          <t>2093</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6629,7 +6629,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1006</t>
+          <t>1088</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5744</t>
+          <t>5747</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,7 +6659,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>52222</t>
+          <t>52588</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>56747</t>
+          <t>56613</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>59506</t>
+          <t>59351</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>113211</t>
+          <t>113208</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>117949</t>
+          <t>117867</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6777,7 +6777,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,08%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2338</t>
+          <t>2620</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10047</t>
+          <t>10254</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3303</t>
+          <t>3680</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13250</t>
+          <t>13374</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7318</t>
+          <t>7346</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19821</t>
+          <t>20217</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,91%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>149252</t>
+          <t>149045</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>156961</t>
+          <t>156679</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>169304</t>
+          <t>169180</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>179251</t>
+          <t>178874</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>322032</t>
+          <t>321636</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>334535</t>
+          <t>334507</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,85%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4184</t>
+          <t>3990</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13371</t>
+          <t>13300</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7728</t>
+          <t>8057</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21648</t>
+          <t>20894</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14680</t>
+          <t>14622</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30536</t>
+          <t>30558</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,91%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>160517</t>
+          <t>160588</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>169704</t>
+          <t>169898</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>190842</t>
+          <t>191596</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>204762</t>
+          <t>204433</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>355842</t>
+          <t>355820</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>371698</t>
+          <t>371756</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,22%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11751</t>
+          <t>11886</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26635</t>
+          <t>27293</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15827</t>
+          <t>15537</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41236</t>
+          <t>40506</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31708</t>
+          <t>32349</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>60549</t>
+          <t>60675</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,44%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>248823</t>
+          <t>248165</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>263707</t>
+          <t>263572</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>264247</t>
+          <t>264977</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>289656</t>
+          <t>289946</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>86,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>520391</t>
+          <t>520265</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>549232</t>
+          <t>548591</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,43%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>24780</t>
+          <t>26360</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>44047</t>
+          <t>45360</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>34970</t>
+          <t>34286</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>62420</t>
+          <t>61958</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>65572</t>
+          <t>63892</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>100011</t>
+          <t>99037</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,93%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>622108</t>
+          <t>620795</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>641375</t>
+          <t>639795</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>699552</t>
+          <t>700014</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>727002</t>
+          <t>727686</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1328116</t>
+          <t>1329090</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1362555</t>
+          <t>1364235</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,53%</t>
         </is>
       </c>
     </row>
